--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1026,7 +1026,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-03: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 1 from the home-page panel (2026-10-03..2026-10-03). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-05: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 2 from the home-page panel (2026-10-03..2026-10-05). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2213,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>2009.3</v>
+        <v>2028.5</v>
       </c>
       <c r="C33" t="n">
-        <v>2433</v>
+        <v>2474</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O873"/>
+  <dimension ref="A1:O874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45031,6 +45031,52 @@
         <v>48508</v>
       </c>
       <c r="O873" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B874" t="n">
+        <v>62588</v>
+      </c>
+      <c r="C874" t="n">
+        <v>62588</v>
+      </c>
+      <c r="D874" t="n">
+        <v>9070</v>
+      </c>
+      <c r="E874" t="n">
+        <v>8987</v>
+      </c>
+      <c r="F874" t="n">
+        <v>44531</v>
+      </c>
+      <c r="G874" t="n">
+        <v>274</v>
+      </c>
+      <c r="H874" t="n">
+        <v>13717</v>
+      </c>
+      <c r="I874" t="n">
+        <v>-13443</v>
+      </c>
+      <c r="J874" t="n">
+        <v>62862</v>
+      </c>
+      <c r="K874" t="n">
+        <v>49145</v>
+      </c>
+      <c r="L874" t="n">
+        <v>320</v>
+      </c>
+      <c r="N874" t="n">
+        <v>49465</v>
+      </c>
+      <c r="O874" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45047,7 +45093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K873"/>
+  <dimension ref="A1:K874"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73934,6 +73980,17 @@
         <v>2009.3</v>
       </c>
     </row>
+    <row r="874">
+      <c r="A874" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B874" t="n">
+        <v>2515</v>
+      </c>
+      <c r="E874" t="n">
+        <v>2047.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1026,7 +1026,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-05: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 2 from the home-page panel (2026-10-03..2026-10-05). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-06: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 3 from the home-page panel (2026-10-03..2026-10-06). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2213,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>2028.5</v>
+        <v>2028.9</v>
       </c>
       <c r="C33" t="n">
-        <v>2474</v>
+        <v>2441.333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O874"/>
+  <dimension ref="A1:O875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45077,6 +45077,52 @@
         <v>49465</v>
       </c>
       <c r="O874" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B875" t="n">
+        <v>60489</v>
+      </c>
+      <c r="C875" t="n">
+        <v>60489</v>
+      </c>
+      <c r="D875" t="n">
+        <v>8747</v>
+      </c>
+      <c r="E875" t="n">
+        <v>6553</v>
+      </c>
+      <c r="F875" t="n">
+        <v>45189</v>
+      </c>
+      <c r="G875" t="n">
+        <v>388</v>
+      </c>
+      <c r="H875" t="n">
+        <v>12165</v>
+      </c>
+      <c r="I875" t="n">
+        <v>-11777</v>
+      </c>
+      <c r="J875" t="n">
+        <v>60877</v>
+      </c>
+      <c r="K875" t="n">
+        <v>48712</v>
+      </c>
+      <c r="L875" t="n">
+        <v>80</v>
+      </c>
+      <c r="N875" t="n">
+        <v>48792</v>
+      </c>
+      <c r="O875" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45093,7 +45139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K874"/>
+  <dimension ref="A1:K875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73991,6 +74037,17 @@
         <v>2047.7</v>
       </c>
     </row>
+    <row r="875">
+      <c r="A875" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B875" t="n">
+        <v>2376</v>
+      </c>
+      <c r="E875" t="n">
+        <v>2029.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1026,7 +1026,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-06: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 3 from the home-page panel (2026-10-03..2026-10-06). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-07: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 4 from the home-page panel (2026-10-03..2026-10-07). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2213,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>2028.9</v>
+        <v>2013.25</v>
       </c>
       <c r="C33" t="n">
-        <v>2441.333333333333</v>
+        <v>2419.5</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O875"/>
+  <dimension ref="A1:O876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45123,6 +45123,52 @@
         <v>48792</v>
       </c>
       <c r="O875" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B876" t="n">
+        <v>68283</v>
+      </c>
+      <c r="C876" t="n">
+        <v>68283</v>
+      </c>
+      <c r="D876" t="n">
+        <v>8643</v>
+      </c>
+      <c r="E876" t="n">
+        <v>14094</v>
+      </c>
+      <c r="F876" t="n">
+        <v>45546</v>
+      </c>
+      <c r="G876" t="n">
+        <v>67</v>
+      </c>
+      <c r="H876" t="n">
+        <v>21159</v>
+      </c>
+      <c r="I876" t="n">
+        <v>-21092</v>
+      </c>
+      <c r="J876" t="n">
+        <v>68350</v>
+      </c>
+      <c r="K876" t="n">
+        <v>47191</v>
+      </c>
+      <c r="L876" t="n">
+        <v>120</v>
+      </c>
+      <c r="N876" t="n">
+        <v>47311</v>
+      </c>
+      <c r="O876" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45139,7 +45185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K875"/>
+  <dimension ref="A1:K876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74048,6 +74094,17 @@
         <v>2029.7</v>
       </c>
     </row>
+    <row r="876">
+      <c r="A876" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B876" t="n">
+        <v>2354</v>
+      </c>
+      <c r="E876" t="n">
+        <v>1966.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -157,6 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Nepal power generation (NEA Load Dispatch Centre, hydro) (to Nov/24)</a:t>
             </a:r>
           </a:p>
@@ -460,6 +461,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Nepal peak demand (NEA LDC) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -1026,7 +1028,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-07: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 4 from the home-page panel (2026-10-03..2026-10-07). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-08: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 5 from the home-page panel (2026-10-03..2026-10-08). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2213,10 +2215,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>2013.25</v>
+        <v>1987.34</v>
       </c>
       <c r="C33" t="n">
-        <v>2419.5</v>
+        <v>2371.4</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O876"/>
+  <dimension ref="A1:O877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45169,6 +45171,52 @@
         <v>47311</v>
       </c>
       <c r="O876" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B877" t="n">
+        <v>66710</v>
+      </c>
+      <c r="C877" t="n">
+        <v>66710</v>
+      </c>
+      <c r="D877" t="n">
+        <v>8582</v>
+      </c>
+      <c r="E877" t="n">
+        <v>13917</v>
+      </c>
+      <c r="F877" t="n">
+        <v>44211</v>
+      </c>
+      <c r="G877" t="n">
+        <v>0</v>
+      </c>
+      <c r="H877" t="n">
+        <v>21502</v>
+      </c>
+      <c r="I877" t="n">
+        <v>-21502</v>
+      </c>
+      <c r="J877" t="n">
+        <v>66710</v>
+      </c>
+      <c r="K877" t="n">
+        <v>45208</v>
+      </c>
+      <c r="L877" t="n">
+        <v>110</v>
+      </c>
+      <c r="N877" t="n">
+        <v>45318</v>
+      </c>
+      <c r="O877" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45185,7 +45233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K876"/>
+  <dimension ref="A1:K877"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74105,6 +74153,17 @@
         <v>1966.3</v>
       </c>
     </row>
+    <row r="877">
+      <c r="A877" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B877" t="n">
+        <v>2179</v>
+      </c>
+      <c r="E877" t="n">
+        <v>1883.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1028,7 +1028,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-08: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 5 from the home-page panel (2026-10-03..2026-10-08). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-09: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 6 from the home-page panel (2026-10-03..2026-10-09). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2215,10 +2215,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>1987.34</v>
+        <v>1963.65</v>
       </c>
       <c r="C33" t="n">
-        <v>2371.4</v>
+        <v>2335.666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O877"/>
+  <dimension ref="A1:O878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45217,6 +45217,52 @@
         <v>45318</v>
       </c>
       <c r="O877" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B878" t="n">
+        <v>67240</v>
+      </c>
+      <c r="C878" t="n">
+        <v>67240</v>
+      </c>
+      <c r="D878" t="n">
+        <v>8578</v>
+      </c>
+      <c r="E878" t="n">
+        <v>14178</v>
+      </c>
+      <c r="F878" t="n">
+        <v>44484</v>
+      </c>
+      <c r="G878" t="n">
+        <v>0</v>
+      </c>
+      <c r="H878" t="n">
+        <v>22953</v>
+      </c>
+      <c r="I878" t="n">
+        <v>-22953</v>
+      </c>
+      <c r="J878" t="n">
+        <v>67240</v>
+      </c>
+      <c r="K878" t="n">
+        <v>44286</v>
+      </c>
+      <c r="L878" t="n">
+        <v>80</v>
+      </c>
+      <c r="N878" t="n">
+        <v>44366</v>
+      </c>
+      <c r="O878" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45233,7 +45279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K877"/>
+  <dimension ref="A1:K878"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74164,6 +74210,17 @@
         <v>1883.7</v>
       </c>
     </row>
+    <row r="878">
+      <c r="A878" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B878" t="n">
+        <v>2157</v>
+      </c>
+      <c r="E878" t="n">
+        <v>1845.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1017,7 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1032,7 +1032,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1107,7 +1106,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B2" t="n">
@@ -1133,7 +1132,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B3" t="n">
@@ -1159,7 +1158,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B4" t="n">
@@ -1185,7 +1184,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B5" t="n">
@@ -1211,7 +1210,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B6" t="n">
@@ -1237,7 +1236,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B7" t="n">
@@ -1263,7 +1262,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B8" t="n">
@@ -1289,7 +1288,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B9" t="n">
@@ -1315,7 +1314,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B10" t="n">
@@ -1341,7 +1340,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B11" t="n">
@@ -1367,7 +1366,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B12" t="n">
@@ -1393,7 +1392,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B13" t="n">
@@ -1419,7 +1418,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B14" t="n">
@@ -1445,7 +1444,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B15" t="n">
@@ -1471,7 +1470,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B16" t="n">
@@ -1497,7 +1496,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B17" t="n">
@@ -1523,7 +1522,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B18" t="n">
@@ -1549,7 +1548,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B19" t="n">
@@ -1575,7 +1574,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B20" t="n">
@@ -1601,7 +1600,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B21" t="n">
@@ -1627,7 +1626,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B22" t="n">
@@ -1653,7 +1652,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B23" t="n">
@@ -1679,7 +1678,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B24" t="n">
@@ -1705,7 +1704,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B25" t="n">
@@ -1731,7 +1730,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B26" t="n">
@@ -1757,7 +1756,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B27" t="n">
@@ -1783,7 +1782,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B28" t="n">
@@ -1809,7 +1808,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B29" t="n">
@@ -1870,7 +1869,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B2" t="n">
@@ -1881,7 +1880,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B3" t="n">
@@ -1892,7 +1891,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B4" t="n">
@@ -1903,18 +1902,18 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B5" t="n">
-        <v>1037.723333333333</v>
+        <v>1037.723333333334</v>
       </c>
       <c r="C5" t="n">
         <v>1330.066666666667</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B6" t="n">
@@ -1925,7 +1924,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B7" t="n">
@@ -1936,18 +1935,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B8" t="n">
-        <v>1235.413793103448</v>
+        <v>1235.413793103449</v>
       </c>
       <c r="C8" t="n">
         <v>1715.827586206897</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B9" t="n">
@@ -1958,7 +1957,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B10" t="n">
@@ -1969,7 +1968,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B11" t="n">
@@ -1980,18 +1979,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B12" t="n">
-        <v>1414.896774193548</v>
+        <v>1414.896774193549</v>
       </c>
       <c r="C12" t="n">
         <v>1709.483870967742</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B13" t="n">
@@ -2002,7 +2001,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B14" t="n">
@@ -2013,7 +2012,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B15" t="n">
@@ -2024,7 +2023,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B16" t="n">
@@ -2035,7 +2034,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B17" t="n">
@@ -2046,7 +2045,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B18" t="n">
@@ -2057,7 +2056,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B19" t="n">
@@ -2068,7 +2067,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B20" t="n">
@@ -2079,7 +2078,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B21" t="n">
@@ -2090,7 +2089,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B22" t="n">
@@ -2101,7 +2100,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B23" t="n">
@@ -2112,18 +2111,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B24" t="n">
-        <v>1554.787096774194</v>
+        <v>1554.787096774193</v>
       </c>
       <c r="C24" t="n">
         <v>1908.677419354839</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B25" t="n">
@@ -2134,18 +2133,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B26" t="n">
-        <v>1641.909677419355</v>
+        <v>1641.909677419354</v>
       </c>
       <c r="C26" t="n">
         <v>1844.129032258065</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B27" t="n">
@@ -2156,7 +2155,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B28" t="n">
@@ -2167,7 +2166,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B29" t="n">
@@ -2178,7 +2177,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B30" t="n">
@@ -2189,7 +2188,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B31" t="n">
@@ -2200,7 +2199,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B32" t="n">
@@ -2211,7 +2210,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B33" t="n">

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1018,6 +1017,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1028,10 +1028,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-09: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 6 from the home-page panel (2026-10-03..2026-10-09). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
-        </is>
-      </c>
-    </row>
+          <t>Daily from 2022-07-17 to 2026-10-27: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 7 from the home-page panel (2026-10-03..2026-10-27). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1106,7 +1107,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B2" t="n">
@@ -1132,7 +1133,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B3" t="n">
@@ -1158,7 +1159,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B4" t="n">
@@ -1184,7 +1185,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B5" t="n">
@@ -1210,7 +1211,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B6" t="n">
@@ -1236,7 +1237,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B7" t="n">
@@ -1262,7 +1263,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B8" t="n">
@@ -1288,7 +1289,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B9" t="n">
@@ -1314,7 +1315,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B10" t="n">
@@ -1340,7 +1341,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B11" t="n">
@@ -1366,7 +1367,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B12" t="n">
@@ -1392,7 +1393,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B13" t="n">
@@ -1418,7 +1419,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B14" t="n">
@@ -1444,7 +1445,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B15" t="n">
@@ -1470,7 +1471,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B16" t="n">
@@ -1496,7 +1497,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B17" t="n">
@@ -1522,7 +1523,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B18" t="n">
@@ -1548,7 +1549,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B19" t="n">
@@ -1574,7 +1575,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B20" t="n">
@@ -1600,7 +1601,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B21" t="n">
@@ -1626,7 +1627,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B22" t="n">
@@ -1652,7 +1653,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B23" t="n">
@@ -1678,7 +1679,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B24" t="n">
@@ -1704,7 +1705,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B25" t="n">
@@ -1730,7 +1731,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B26" t="n">
@@ -1756,7 +1757,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B27" t="n">
@@ -1782,7 +1783,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B28" t="n">
@@ -1808,7 +1809,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B29" t="n">
@@ -1869,7 +1870,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B2" t="n">
@@ -1880,7 +1881,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B3" t="n">
@@ -1891,7 +1892,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B4" t="n">
@@ -1902,7 +1903,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B5" t="n">
@@ -1913,7 +1914,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B6" t="n">
@@ -1924,7 +1925,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B7" t="n">
@@ -1935,7 +1936,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44927</v>
       </c>
       <c r="B8" t="n">
@@ -1946,7 +1947,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44958</v>
       </c>
       <c r="B9" t="n">
@@ -1957,7 +1958,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B10" t="n">
@@ -1968,7 +1969,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B11" t="n">
@@ -1979,7 +1980,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B12" t="n">
@@ -1990,7 +1991,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B13" t="n">
@@ -2001,7 +2002,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B14" t="n">
@@ -2012,7 +2013,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B15" t="n">
@@ -2023,7 +2024,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B16" t="n">
@@ -2034,7 +2035,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B17" t="n">
@@ -2045,7 +2046,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B18" t="n">
@@ -2056,7 +2057,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B19" t="n">
@@ -2067,7 +2068,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B20" t="n">
@@ -2078,7 +2079,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>45323</v>
       </c>
       <c r="B21" t="n">
@@ -2089,7 +2090,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B22" t="n">
@@ -2100,7 +2101,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B23" t="n">
@@ -2111,7 +2112,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B24" t="n">
@@ -2122,7 +2123,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B25" t="n">
@@ -2133,7 +2134,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B26" t="n">
@@ -2144,7 +2145,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B27" t="n">
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B28" t="n">
@@ -2166,7 +2167,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B29" t="n">
@@ -2177,7 +2178,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B30" t="n">
@@ -2188,7 +2189,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B31" t="n">
@@ -2199,7 +2200,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45658</v>
       </c>
       <c r="B32" t="n">
@@ -2210,14 +2211,14 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>1963.65</v>
+        <v>1911.857142857143</v>
       </c>
       <c r="C33" t="n">
-        <v>2335.666666666667</v>
+        <v>2302</v>
       </c>
     </row>
   </sheetData>
@@ -2232,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O878"/>
+  <dimension ref="A1:O879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45262,6 +45263,52 @@
         <v>44366</v>
       </c>
       <c r="O878" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B879" t="n">
+        <v>63612</v>
+      </c>
+      <c r="C879" t="n">
+        <v>63612</v>
+      </c>
+      <c r="D879" t="n">
+        <v>7981</v>
+      </c>
+      <c r="E879" t="n">
+        <v>11268</v>
+      </c>
+      <c r="F879" t="n">
+        <v>44363</v>
+      </c>
+      <c r="G879" t="n">
+        <v>0</v>
+      </c>
+      <c r="H879" t="n">
+        <v>25185</v>
+      </c>
+      <c r="I879" t="n">
+        <v>-25185</v>
+      </c>
+      <c r="J879" t="n">
+        <v>63612</v>
+      </c>
+      <c r="K879" t="n">
+        <v>38426</v>
+      </c>
+      <c r="L879" t="n">
+        <v>0</v>
+      </c>
+      <c r="N879" t="n">
+        <v>38426</v>
+      </c>
+      <c r="O879" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45278,7 +45325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K878"/>
+  <dimension ref="A1:K879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74220,6 +74267,17 @@
         <v>1845.2</v>
       </c>
     </row>
+    <row r="879">
+      <c r="A879" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B879" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E879" t="n">
+        <v>1601.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -2215,10 +2215,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>1911.857142857143</v>
+        <v>1930.057142857143</v>
       </c>
       <c r="C33" t="n">
-        <v>2302</v>
+        <v>2316.285714285714</v>
       </c>
     </row>
   </sheetData>
@@ -45273,40 +45273,40 @@
         <v>46322</v>
       </c>
       <c r="B879" t="n">
-        <v>63612</v>
+        <v>61240</v>
       </c>
       <c r="C879" t="n">
-        <v>63612</v>
+        <v>61240</v>
       </c>
       <c r="D879" t="n">
-        <v>7981</v>
+        <v>8168</v>
       </c>
       <c r="E879" t="n">
-        <v>11268</v>
+        <v>8359</v>
       </c>
       <c r="F879" t="n">
-        <v>44363</v>
+        <v>44713</v>
       </c>
       <c r="G879" t="n">
         <v>0</v>
       </c>
       <c r="H879" t="n">
-        <v>25185</v>
+        <v>19755</v>
       </c>
       <c r="I879" t="n">
-        <v>-25185</v>
+        <v>-19755</v>
       </c>
       <c r="J879" t="n">
-        <v>63612</v>
+        <v>61240</v>
       </c>
       <c r="K879" t="n">
-        <v>38426</v>
+        <v>41485</v>
       </c>
       <c r="L879" t="n">
         <v>0</v>
       </c>
       <c r="N879" t="n">
-        <v>38426</v>
+        <v>41485</v>
       </c>
       <c r="O879" t="inlineStr">
         <is>
@@ -74272,10 +74272,10 @@
         <v>46322</v>
       </c>
       <c r="B879" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="E879" t="n">
-        <v>1601.1</v>
+        <v>1728.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1028,7 +1028,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-27: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 7 from the home-page panel (2026-10-03..2026-10-27). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-28: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 8 from the home-page panel (2026-10-03..2026-10-28). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2215,10 +2215,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>1930.057142857143</v>
+        <v>1901.7625</v>
       </c>
       <c r="C33" t="n">
-        <v>2316.285714285714</v>
+        <v>2308.875</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O879"/>
+  <dimension ref="A1:O880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45309,6 +45309,52 @@
         <v>41485</v>
       </c>
       <c r="O879" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B880" t="n">
+        <v>60947</v>
+      </c>
+      <c r="C880" t="n">
+        <v>60947</v>
+      </c>
+      <c r="D880" t="n">
+        <v>8457</v>
+      </c>
+      <c r="E880" t="n">
+        <v>9057</v>
+      </c>
+      <c r="F880" t="n">
+        <v>43433</v>
+      </c>
+      <c r="G880" t="n">
+        <v>0</v>
+      </c>
+      <c r="H880" t="n">
+        <v>20059</v>
+      </c>
+      <c r="I880" t="n">
+        <v>-20059</v>
+      </c>
+      <c r="J880" t="n">
+        <v>60947</v>
+      </c>
+      <c r="K880" t="n">
+        <v>40889</v>
+      </c>
+      <c r="L880" t="n">
+        <v>0</v>
+      </c>
+      <c r="N880" t="n">
+        <v>40889</v>
+      </c>
+      <c r="O880" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45325,7 +45371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K879"/>
+  <dimension ref="A1:K880"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74278,6 +74324,17 @@
         <v>1728.5</v>
       </c>
     </row>
+    <row r="880">
+      <c r="A880" s="4" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B880" t="n">
+        <v>2257</v>
+      </c>
+      <c r="E880" t="n">
+        <v>1703.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/nepal_power_generation_daily.xlsx
@@ -1028,7 +1028,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daily from 2022-07-17 to 2026-10-28: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 8 from the home-page panel (2026-10-03..2026-10-28). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
+          <t>Daily from 2022-07-17 to 2026-10-29: 604 days from reports (2023-04-14..2025-01-11), 267 from monthly reports (2022-07-17..2024-02-08), 9 from the home-page panel (2026-10-03..2026-10-29). NEA's published report archive covers 2080-01-01..2081-09-27 BS (14 Apr 2023 - 11 Jan 2025) with a few days missing; the monthly reports (NMOR, daily rows) cover Shrawan 2079 - Falgun 2080 BS (Jul 2022 - Mar 2024). Nothing earlier is online since NEA's site moved, and nothing after Jan 2025 has been posted (checked: daily, monthly and yearly categories, Oct 2026). Days between the end of the archive and the first panel snapshot are empty.</t>
         </is>
       </c>
     </row>
@@ -2215,10 +2215,10 @@
         <v>46296</v>
       </c>
       <c r="B33" t="n">
-        <v>1901.7625</v>
+        <v>1880.788888888889</v>
       </c>
       <c r="C33" t="n">
-        <v>2308.875</v>
+        <v>2293.111111111111</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O880"/>
+  <dimension ref="A1:O881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45355,6 +45355,52 @@
         <v>40889</v>
       </c>
       <c r="O880" t="inlineStr">
+        <is>
+          <t>NEA home page (latest day)</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B881" t="n">
+        <v>60015</v>
+      </c>
+      <c r="C881" t="n">
+        <v>60015</v>
+      </c>
+      <c r="D881" t="n">
+        <v>8568</v>
+      </c>
+      <c r="E881" t="n">
+        <v>8123</v>
+      </c>
+      <c r="F881" t="n">
+        <v>43324</v>
+      </c>
+      <c r="G881" t="n">
+        <v>0</v>
+      </c>
+      <c r="H881" t="n">
+        <v>18901</v>
+      </c>
+      <c r="I881" t="n">
+        <v>-18901</v>
+      </c>
+      <c r="J881" t="n">
+        <v>60015</v>
+      </c>
+      <c r="K881" t="n">
+        <v>41113</v>
+      </c>
+      <c r="L881" t="n">
+        <v>0</v>
+      </c>
+      <c r="N881" t="n">
+        <v>41113</v>
+      </c>
+      <c r="O881" t="inlineStr">
         <is>
           <t>NEA home page (latest day)</t>
         </is>
@@ -45371,7 +45417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K880"/>
+  <dimension ref="A1:K881"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74335,6 +74381,17 @@
         <v>1703.7</v>
       </c>
     </row>
+    <row r="881">
+      <c r="A881" s="4" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B881" t="n">
+        <v>2167</v>
+      </c>
+      <c r="E881" t="n">
+        <v>1713</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
